--- a/results/job_matches_2026-07-04.xlsx
+++ b/results/job_matches_2026-07-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,52 +538,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7dce5ca3032b2ad</t>
+          <t>https://www.indeed.com/viewjob?jk=85da536c77d90e54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Career Team Enterprises</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90b2f930cb110ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=78392f2d9015aeeb</t>
         </is>
       </c>
     </row>
@@ -613,125 +613,125 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>QUARTERMASTER</t>
+          <t>Climb</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Cloud Storage, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926718992d1fd024</t>
+          <t>https://www.indeed.com/viewjob?jk=f49fab7756cd40ca</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT Architect (ADI)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Climb</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9d3910b5fff7ee</t>
+          <t>https://www.indeed.com/viewjob?jk=64b506ee2b284700</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Remote)</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78392f2d9015aeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Climb</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f49fab7756cd40ca</t>
+          <t>https://www.indeed.com/viewjob?jk=92331c671f336d40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Climb</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, API Gateway, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b506ee2b284700</t>
+          <t>https://www.indeed.com/viewjob?jk=22049ffcc6bb4062</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>CADRE GOVERNMENT SOLUTIONS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=e2099b5430245346</t>
         </is>
       </c>
     </row>
@@ -823,20 +823,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hudson River Community Credit Union</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Corinth, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,84 +846,84 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92331c671f336d40</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7fcbb496808adb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer II - Python</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Civil Liberties Union</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
+          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer / BI Developer (GCP, Power BI, Tableau)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8537a55ac652d5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,15 +933,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, Airflow, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22049ffcc6bb4062</t>
+          <t>https://www.indeed.com/viewjob?jk=cc379557ac7b50a7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2099b5430245346</t>
+          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Big Data / AWS Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, Scala, CI/CD</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=33f34675d6b944c5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect - Long Beach, CA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hudson River Community Credit Union</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Corinth, NY, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7fcbb496808adb</t>
+          <t>https://www.indeed.com/viewjob?jk=67e127e3639656d8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Hillman Group</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Architect – AWS &amp; Data Governance | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tricon Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, Airflow, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc379557ac7b50a7</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d27ed14ea847a8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
+          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Data Architect and Engineer</t>
+          <t>Group AI/ML Sol Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Logisnext Americas Inc</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Data Architect and Engineer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Logisnext Americas Inc</t>
+          <t>Awesome Motive Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
+          <t>https://www.indeed.com/viewjob?jk=98f33599b59c5df8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f34675d6b944c5</t>
+          <t>https://www.indeed.com/viewjob?jk=7ffad5f6aac08e5a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer</t>
+          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,427 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Genpact</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Gordon Food Service</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Wyoming, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Gordon Food Service</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Auburn Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Snowflake Architect – AWS &amp; Data Governance | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Tricon Solutions</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d27ed14ea847a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Data Analyst / Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>McAfee</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Whatfix</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>General Dynamics Information Technology</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Chantilly, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Whatfix</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ffad5f6aac08e5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Awesome Motive Inc.</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Miami Beach, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98f33599b59c5df8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-04.xlsx
+++ b/results/job_matches_2026-07-04.xlsx
@@ -503,52 +503,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DBT Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OSI Digital</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>13.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Google Cloud Platform, Scala, Snowflake, Time Travel, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8765bd1c65b5570</t>
+          <t>https://www.indeed.com/viewjob?jk=85da536c77d90e54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85da536c77d90e54</t>
+          <t>https://www.indeed.com/viewjob?jk=78392f2d9015aeeb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Climb</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78392f2d9015aeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=f49fab7756cd40ca</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f49fab7756cd40ca</t>
+          <t>https://www.indeed.com/viewjob?jk=64b506ee2b284700</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Climb</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,59 +661,59 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b506ee2b284700</t>
+          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=92331c671f336d40</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92331c671f336d40</t>
+          <t>https://www.indeed.com/viewjob?jk=22049ffcc6bb4062</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CADRE GOVERNMENT SOLUTIONS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22049ffcc6bb4062</t>
+          <t>https://www.indeed.com/viewjob?jk=e2099b5430245346</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
+          <t>Hudson River Community Credit Union</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Corinth, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2099b5430245346</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7fcbb496808adb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - Python</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hudson River Community Credit Union</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Corinth, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7fcbb496808adb</t>
+          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python</t>
+          <t>Senior Software Engineer - SRE Focus</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9b9608e126cebe</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Architect - Long Beach, CA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f34675d6b944c5</t>
+          <t>https://www.indeed.com/viewjob?jk=67e127e3639656d8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Long Beach, CA</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, dbt</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67e127e3639656d8</t>
+          <t>https://www.indeed.com/viewjob?jk=33f34675d6b944c5</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
+          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ffad5f6aac08e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
+          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=7ffad5f6aac08e5a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-04.xlsx
+++ b/results/job_matches_2026-07-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Climb</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78392f2d9015aeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=f49fab7756cd40ca</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f49fab7756cd40ca</t>
+          <t>https://www.indeed.com/viewjob?jk=64b506ee2b284700</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Climb</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b506ee2b284700</t>
+          <t>https://www.indeed.com/viewjob?jk=92331c671f336d40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=22049ffcc6bb4062</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CADRE GOVERNMENT SOLUTIONS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92331c671f336d40</t>
+          <t>https://www.indeed.com/viewjob?jk=e2099b5430245346</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hudson River Community Credit Union</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Corinth, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22049ffcc6bb4062</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7fcbb496808adb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Software Engineer II - Python</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2099b5430245346</t>
+          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - SRE Focus</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hudson River Community Credit Union</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Corinth, NY, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7fcbb496808adb</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9b9608e126cebe</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python</t>
+          <t>Senior Software Engineer / BI Developer (GCP, Power BI, Tableau)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8537a55ac652d5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE Focus</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, Airflow, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9b9608e126cebe</t>
+          <t>https://www.indeed.com/viewjob?jk=cc379557ac7b50a7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer / BI Developer (GCP, Power BI, Tableau)</t>
+          <t>Senior Data Architect - Long Beach, CA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8537a55ac652d5</t>
+          <t>https://www.indeed.com/viewjob?jk=67e127e3639656d8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, Airflow, Python</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc379557ac7b50a7</t>
+          <t>https://www.indeed.com/viewjob?jk=33f34675d6b944c5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Long Beach, CA</t>
+          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67e127e3639656d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Snowflake Architect – AWS &amp; Data Governance | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>Tricon Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f34675d6b944c5</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d27ed14ea847a8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
+          <t>Group AI/ML Sol Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
+          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer</t>
+          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
+          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Snowflake Architect – AWS &amp; Data Governance | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tricon Solutions</t>
+          <t>Awesome Motive Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d27ed14ea847a8</t>
+          <t>https://www.indeed.com/viewjob?jk=98f33599b59c5df8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,155 +1186,15 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Group AI/ML Sol Architect - PostgreSQL</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>HCLTech</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Virginia Beach, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Awesome Motive Inc.</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Miami Beach, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98f33599b59c5df8</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Whatfix</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Whatfix</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7ffad5f6aac08e5a</t>
         </is>

--- a/results/job_matches_2026-07-04.xlsx
+++ b/results/job_matches_2026-07-04.xlsx
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer</t>
+          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
+          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Whatfix</t>
+          <t>Awesome Motive Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Miami Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=98f33599b59c5df8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Awesome Motive Inc.</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Miami Beach, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f33599b59c5df8</t>
+          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-04.xlsx
+++ b/results/job_matches_2026-07-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
+          <t>https://www.indeed.com/viewjob?jk=02cd4ab61a45abcd</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer</t>
+          <t>Snowflake Architect – AWS &amp; Data Governance | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Tricon Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d27ed14ea847a8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Snowflake Architect – AWS &amp; Data Governance | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
+          <t>Group AI/ML Sol Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tricon Solutions</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d27ed14ea847a8</t>
+          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Group AI/ML Sol Architect - PostgreSQL</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Awesome Motive Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Miami Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
+          <t>https://www.indeed.com/viewjob?jk=98f33599b59c5df8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Awesome Motive Inc.</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Miami Beach, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f33599b59c5df8</t>
+          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
+          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1160,41 +1160,6 @@
         </is>
       </c>
       <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Whatfix</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7ffad5f6aac08e5a</t>
         </is>

--- a/results/job_matches_2026-07-04.xlsx
+++ b/results/job_matches_2026-07-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Altak Group</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>13.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3375df1916d0dbd2</t>
+          <t>https://www.indeed.com/viewjob?jk=85da536c77d90e54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Climb</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85da536c77d90e54</t>
+          <t>https://www.indeed.com/viewjob?jk=f49fab7756cd40ca</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f49fab7756cd40ca</t>
+          <t>https://www.indeed.com/viewjob?jk=64b506ee2b284700</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Climb</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b506ee2b284700</t>
+          <t>https://www.indeed.com/viewjob?jk=92331c671f336d40</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92331c671f336d40</t>
+          <t>https://www.indeed.com/viewjob?jk=22049ffcc6bb4062</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CADRE GOVERNMENT SOLUTIONS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22049ffcc6bb4062</t>
+          <t>https://www.indeed.com/viewjob?jk=e2099b5430245346</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
+          <t>Hudson River Community Credit Union</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Corinth, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2099b5430245346</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7fcbb496808adb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hudson River Community Credit Union</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Corinth, NY, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7fcbb496808adb</t>
+          <t>https://www.indeed.com/viewjob?jk=02cd4ab61a45abcd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Senior Software Engineer - SRE Focus</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02cd4ab61a45abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9b9608e126cebe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE Focus</t>
+          <t>Senior Software Engineer / BI Developer (GCP, Power BI, Tableau)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9b9608e126cebe</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8537a55ac652d5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer / BI Developer (GCP, Power BI, Tableau)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, Airflow, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8537a55ac652d5</t>
+          <t>https://www.indeed.com/viewjob?jk=cc379557ac7b50a7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, Airflow, Python</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc379557ac7b50a7</t>
+          <t>https://www.indeed.com/viewjob?jk=33f34675d6b944c5</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f34675d6b944c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer</t>
+          <t>Snowflake Architect – AWS &amp; Data Governance | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Tricon Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d27ed14ea847a8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Snowflake Architect – AWS &amp; Data Governance | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
+          <t>Group AI/ML Sol Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tricon Solutions</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d27ed14ea847a8</t>
+          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Group AI/ML Sol Architect - PostgreSQL</t>
+          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
+          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
+          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
+          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1125,41 +1125,6 @@
         </is>
       </c>
       <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Whatfix</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7ffad5f6aac08e5a</t>
         </is>

--- a/results/job_matches_2026-07-04.xlsx
+++ b/results/job_matches_2026-07-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, Airflow, Python</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc379557ac7b50a7</t>
+          <t>https://www.indeed.com/viewjob?jk=33f34675d6b944c5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Architect - Long Beach, CA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f34675d6b944c5</t>
+          <t>https://www.indeed.com/viewjob?jk=67e127e3639656d8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Long Beach, CA</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67e127e3639656d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer</t>
+          <t>Snowflake Architect – AWS &amp; Data Governance | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Tricon Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d27ed14ea847a8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Snowflake Architect – AWS &amp; Data Governance | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
+          <t>Group AI/ML Sol Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tricon Solutions</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d27ed14ea847a8</t>
+          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Group AI/ML Sol Architect - PostgreSQL</t>
+          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,24 +1011,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
+          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
+          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
+          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1055,76 +1055,6 @@
         </is>
       </c>
       <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Awesome Motive Inc.</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Miami Beach, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98f33599b59c5df8</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Whatfix</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7ffad5f6aac08e5a</t>
         </is>

--- a/results/job_matches_2026-07-04.xlsx
+++ b/results/job_matches_2026-07-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hudson River Community Credit Union</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Corinth, NY, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7fcbb496808adb</t>
+          <t>https://www.indeed.com/viewjob?jk=02cd4ab61a45abcd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Senior Software Engineer / BI Developer (GCP, Power BI, Tableau)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02cd4ab61a45abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8537a55ac652d5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE Focus</t>
+          <t>Senior Data Architect - Long Beach, CA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9b9608e126cebe</t>
+          <t>https://www.indeed.com/viewjob?jk=67e127e3639656d8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer / BI Developer (GCP, Power BI, Tableau)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, Power BI, Tableau, Python</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8537a55ac652d5</t>
+          <t>https://www.indeed.com/viewjob?jk=33f34675d6b944c5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f34675d6b944c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Long Beach, CA</t>
+          <t>Snowflake Architect – AWS &amp; Data Governance | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Tricon Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67e127e3639656d8</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d27ed14ea847a8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer</t>
+          <t>Group AI/ML Sol Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
+          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Snowflake Architect – AWS &amp; Data Governance | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
+          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tricon Solutions</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d27ed14ea847a8</t>
+          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Group AI/ML Sol Architect - PostgreSQL</t>
+          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,85 +976,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
+          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Whatfix</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Whatfix</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7ffad5f6aac08e5a</t>
         </is>

--- a/results/job_matches_2026-07-04.xlsx
+++ b/results/job_matches_2026-07-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Snowflake Architect – AWS &amp; Data Governance | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
+          <t>Group AI/ML Sol Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tricon Solutions</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d27ed14ea847a8</t>
+          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Group AI/ML Sol Architect - PostgreSQL</t>
+          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,24 +906,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
+          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
+          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
+          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -950,41 +950,6 @@
         </is>
       </c>
       <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Whatfix</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7ffad5f6aac08e5a</t>
         </is>

--- a/results/job_matches_2026-07-04.xlsx
+++ b/results/job_matches_2026-07-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Group AI/ML Sol Architect - PostgreSQL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Nicklaus Children's Health System</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab45996cd47738b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
+          <t>Group AI/ML Sol Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Whatfix</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,52 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Whatfix</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ffad5f6aac08e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-04.xlsx
+++ b/results/job_matches_2026-07-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Climb</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f49fab7756cd40ca</t>
+          <t>https://www.indeed.com/viewjob?jk=92331c671f336d40</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Climb</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, API Gateway, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b506ee2b284700</t>
+          <t>https://www.indeed.com/viewjob?jk=22049ffcc6bb4062</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92331c671f336d40</t>
+          <t>https://www.indeed.com/viewjob?jk=02cd4ab61a45abcd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer / BI Developer (GCP, Power BI, Tableau)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22049ffcc6bb4062</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8537a55ac652d5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Senior Data Architect - Long Beach, CA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2099b5430245346</t>
+          <t>https://www.indeed.com/viewjob?jk=67e127e3639656d8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,215 +706,75 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02cd4ab61a45abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer / BI Developer (GCP, Power BI, Tableau)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Nicklaus Children's Health System</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, Power BI, Tableau, Python</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8537a55ac652d5</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab45996cd47738b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Long Beach, CA</t>
+          <t>Group AI/ML Sol Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67e127e3639656d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>OnMed</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>White Plains, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33f34675d6b944c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Quality Assurance Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Pearson</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Nicklaus Children's Health System</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab45996cd47738b</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Group AI/ML Sol Architect - PostgreSQL</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>HCLTech</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Virginia Beach, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
         </is>

--- a/results/job_matches_2026-07-04.xlsx
+++ b/results/job_matches_2026-07-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92331c671f336d40</t>
+          <t>https://www.indeed.com/viewjob?jk=02cd4ab61a45abcd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer / BI Developer (GCP, Power BI, Tableau)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22049ffcc6bb4062</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8537a55ac652d5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Senior Data Architect - Long Beach, CA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,180 +601,75 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02cd4ab61a45abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=67e127e3639656d8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer / BI Developer (GCP, Power BI, Tableau)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Nicklaus Children's Health System</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, Power BI, Tableau, Python</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8537a55ac652d5</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab45996cd47738b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Long Beach, CA</t>
+          <t>Group AI/ML Sol Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67e127e3639656d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Quality Assurance Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Pearson</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Nicklaus Children's Health System</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab45996cd47738b</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Group AI/ML Sol Architect - PostgreSQL</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>HCLTech</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Virginia Beach, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
         </is>

--- a/results/job_matches_2026-07-04.xlsx
+++ b/results/job_matches_2026-07-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85da536c77d90e54</t>
+          <t>https://www.indeed.com/viewjob?jk=02cd4ab61a45abcd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Senior Software Engineer / BI Developer (GCP, Power BI, Tableau)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02cd4ab61a45abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8537a55ac652d5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer / BI Developer (GCP, Power BI, Tableau)</t>
+          <t>Senior Data Architect - Long Beach, CA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8537a55ac652d5</t>
+          <t>https://www.indeed.com/viewjob?jk=67e127e3639656d8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Long Beach, CA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Nicklaus Children's Health System</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, dbt</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67e127e3639656d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab45996cd47738b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Group AI/ML Sol Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nicklaus Children's Health System</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,50 +626,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab45996cd47738b</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Group AI/ML Sol Architect - PostgreSQL</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>HCLTech</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Virginia Beach, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
         </is>
